--- a/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 6  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (21 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
         </is>
       </c>
     </row>
@@ -959,17 +959,17 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Wuffy</t>
+          <t>Loona</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Wuffy Robot Puppy</t>
+          <t>Robot Pet Dog</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>25.99</v>
+        <v>499</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>80</v>
+        <v>1199</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" s="13" t="n">
         <v>3</v>
@@ -996,23 +996,23 @@
         <v>2</v>
       </c>
       <c r="L9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="13" t="n">
+      <c r="O9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O9" s="13" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Loona</t>
+          <t>Ruko</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Robot Pet Dog</t>
+          <t>18011 Smart Robot Dog</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1041,102 +1041,39 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>499</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>1199</v>
+        <v>283</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>3</v>
       </c>
       <c r="O10" s="9" t="n">
         <v>2</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Ruko</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>18011 Smart Robot Dog</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Budget Friendly</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>283</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>

--- a/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
+          <t>Generated: 2026-07-16  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
+          <t>Generated: 2026-08-10  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
         </is>
       </c>
     </row>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>4.5</v>
@@ -858,7 +858,7 @@
         <v>4.3</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>5164</v>
+        <v>5195</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>4.1</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -918,10 +918,10 @@
         <v>44.45</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>553</v>
+        <v>441</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>2.8</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Border Collie' per repo. Review Strength=3: 403 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>499</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I9" s="16" t="n">
         <v>2.5</v>
@@ -1044,10 +1044,10 @@
         <v>69.98999999999999</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="I10" s="15" t="n">
         <v>2.4</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Original Border Collie</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">

--- a/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Dog Owners List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
+          <t>Generated: 2026-08-13  |  Products shown: 5  |  Eliminated by dedup rule: 2  |  Pre-filter: Category equal Dog  (22 products removed)</t>
         </is>
       </c>
     </row>
